--- a/WorkBot/refactor/data/orders/Ithaca Bakery/Ithaca Bakery_Downtown_2025-10-03.xlsx
+++ b/WorkBot/refactor/data/orders/Ithaca Bakery/Ithaca Bakery_Downtown_2025-10-03.xlsx
@@ -683,7 +683,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -693,7 +693,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>33.00</t>
+          <t>49.50</t>
         </is>
       </c>
     </row>
@@ -706,7 +706,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
